--- a/tricount_extractor/tests/data/expected_results/income_trip_7.xlsx
+++ b/tricount_extractor/tests/data/expected_results/income_trip_7.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,45 +514,65 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>created</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>original_amount</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>original_currency</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>payer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>is_reimbursement</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>type_transaction</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
@@ -568,36 +588,54 @@
       <c r="C2" s="1" t="n">
         <v>45658.5</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="n">
+        <v>45658.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Shared Expense</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="F2" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>-40</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="J2" t="b">
+      <c r="K2" t="b">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>FOOD</t>
         </is>
@@ -613,36 +651,54 @@
       <c r="C3" s="1" t="n">
         <v>45659.41666666666</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="1" t="n">
+        <v>45659.41666666666</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Shared Income</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>100</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>100</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="J3" t="b">
+      <c r="K3" t="b">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>INCOME</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>UNCATEGORIZED</t>
         </is>
@@ -658,36 +714,54 @@
       <c r="C4" s="1" t="n">
         <v>45660.375</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="1" t="n">
+        <v>45660.375</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Custom Category Expense</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="F4" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>-30</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="J4" t="b">
+      <c r="K4" t="b">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>custom category</t>
         </is>
@@ -704,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -735,27 +809,42 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>type_transaction</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>participant</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>original_share</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>original_currency</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>split_type</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>share_ratio</t>
         </is>
       </c>
     </row>
@@ -784,24 +873,37 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="I2" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -829,24 +931,37 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>20</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>20</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="I3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -874,24 +989,37 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>INCOME</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>50</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>50</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -919,24 +1047,37 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>INCOME</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>50</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>50</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -964,24 +1105,37 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>Alice</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>15</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="I6" t="n">
+        <v>-15</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1009,24 +1163,37 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>15</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>15</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="I7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
